--- a/accountant-skill/data/Jan2026/adjusting_entries_Jan2026.xlsx
+++ b/accountant-skill/data/Jan2026/adjusting_entries_Jan2026.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>54750</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>87750</v>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>6000</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="20">
@@ -789,16 +789,16 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Bank Recon</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Monthly SL depreciation — Office Equipment</t>
+          <t>Bank recon adj — Bank interest earned</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>7500</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="21">
@@ -814,30 +814,10 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Bank recon adj — Bank interest earned</t>
+          <t>Bank recon adj — Software subscription (auto-debit)</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>ADJ-006</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Bank Recon</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Bank recon adj — Software subscription (auto-debit)</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n">
         <v>18000</v>
       </c>
     </row>
@@ -861,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -870,7 +850,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
@@ -1001,12 +981,12 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>15110</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1028,12 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>15110</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1075,12 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>15210</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1122,12 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>15210</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1169,12 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>15310</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1216,12 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>15310</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1263,12 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>15310</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1310,12 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>15310</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1415,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="F20" s="7" t="n">
@@ -1443,12 +1423,12 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Accum. Depr. — Buildings</t>
+          <t>Accum. Depr. — Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="I20" s="7" t="n">
@@ -1478,7 +1458,7 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="F21" s="7" t="n">
@@ -1486,12 +1466,12 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Accum. Depr. — Plant &amp; Machinery</t>
+          <t>Accum. Depr. — Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="I21" s="7" t="n">
@@ -1521,85 +1501,42 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="F22" s="7" t="n">
-        <v>6000</v>
+        <v>13500</v>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Accum. Depr. — Furniture &amp; Fixtures</t>
+          <t>Accum. Depr. — Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="I22" s="7" t="n">
-        <v>6000</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>ADJ-004</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation — Office Equipment</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation Expense</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>5300</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>7500</v>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Accum. Depr. — Office Equipment</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>1651</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="n">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Total Depreciation</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n">
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n">
         <v>54750</v>
       </c>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n">
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n">
         <v>54750</v>
       </c>
     </row>
@@ -1714,7 +1651,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>ADJ-005</t>
+          <t>ADJ-004</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -1739,7 +1676,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
@@ -1752,7 +1689,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="J6" s="7" t="n">
@@ -1762,7 +1699,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>ADJ-006</t>
+          <t>ADJ-005</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -1787,7 +1724,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="G7" s="7" t="n">
@@ -1800,7 +1737,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="J7" s="7" t="n">
@@ -1936,11 +1873,11 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2030</v>
+        <v>22200</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Accrued Wages</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1965,11 +1902,11 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>2030</v>
+        <v>22200</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Accrued Wages</t>
+          <t>Wages Payable</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -2021,7 +1958,7 @@
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -2107,11 +2044,11 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>1320</v>
+        <v>13000</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Account 1320</t>
+          <t>Account 13000</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -2157,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2167,7 +2104,7 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="37" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
@@ -2280,7 +2217,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
@@ -2288,12 +2225,12 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Accum. Depr. — Buildings</t>
+          <t>Accum. Depr. — Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="J6" s="7" t="n">
@@ -2333,7 +2270,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="G7" s="7" t="n">
@@ -2341,12 +2278,12 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Accum. Depr. — Plant &amp; Machinery</t>
+          <t>Accum. Depr. — Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="J7" s="7" t="n">
@@ -2386,24 +2323,24 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
-        <v>6000</v>
+        <v>13500</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Accum. Depr. — Furniture &amp; Fixtures</t>
+          <t>Accum. Depr. — Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="J8" s="7" t="n">
-        <v>6000</v>
+        <v>13500</v>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
@@ -2424,43 +2361,43 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Bank Recon</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Depreciation — Office Equipment</t>
+          <t>Bank Interest Earned</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Depreciation Expense</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Accum. Depr. — Office Equipment</t>
+          <t>Interest Income</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="J9" s="7" t="n">
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Monthly SL depreciation — Office Equipment</t>
+          <t>Bank recon adj — Bank interest earned</t>
         </is>
       </c>
     </row>
@@ -2482,128 +2419,75 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Bank Interest Earned</t>
+          <t>Software / Subscription</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
+          <t>Telephone &amp; Internet</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>65000</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
           <t>Cash at Bank</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Interest Income</t>
-        </is>
-      </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="J10" s="7" t="n">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Bank recon adj — Bank interest earned</t>
+          <t>Bank recon adj — Software subscription (auto-debit)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>ADJ-006</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Bank Recon</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Software / Subscription</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Telephone &amp; Internet</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>5220</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>18000</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Cash at Bank</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="n">
-        <v>18000</v>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>Bank recon adj — Software subscription (auto-debit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="9" t="n">
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n">
         <v>87750</v>
       </c>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n">
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n">
         <v>87750</v>
       </c>
-      <c r="K12" s="9" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="K11" s="9" t="n"/>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Double-Entry Check</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>Dr 87,750.00 = Cr 87,750.00</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2626,7 +2510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2706,12 +2590,12 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Cash at Bank — Main Account</t>
+          <t>Cash at Bank</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -2740,12 +2624,12 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Buildings</t>
+          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -2774,12 +2658,12 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Plant &amp; Machinery</t>
+          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -2808,12 +2692,12 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Account 1631</t>
+          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -2827,81 +2711,81 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>160000</v>
+        <v>100000</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>6000</v>
+        <v>13500</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>166000</v>
+        <v>113500</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>0.0375</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation — Office Equipment</t>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>100000</v>
+        <v>1468500</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>7500</v>
+        <v>18000</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>107500</v>
+        <v>1486500</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>0.075</v>
+        <v>0.01225740551583248</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Depreciation Expenses - SG&amp;A</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expense</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>15000</v>
+        <v>54750</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>15000</v>
+        <v>54750</v>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
@@ -2912,68 +2796,34 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Telephone &amp; Internet</t>
+          <t>Interest Income</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Expense</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>73000</v>
-      </c>
-      <c r="H12" s="14" t="n">
-        <v>0.3272727272727273</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>5300</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation Expense</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>54750</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>54750</v>
-      </c>
-      <c r="H13" s="15" t="inlineStr">
+        <v>15000</v>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/accountant-skill/data/Jan2026/adjusting_entries_Jan2026.xlsx
+++ b/accountant-skill/data/Jan2026/adjusting_entries_Jan2026.xlsx
@@ -12,8 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank Recon Entries" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accruals" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prepayments" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Entries" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Account Impact" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Entries" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Account Impact" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -132,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -162,6 +163,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -2094,6 +2096,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Inventory — Materials Issued to Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Summary of inventory sub-ledger movements</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01  to  2026-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Materials issued to production are recorded via inventory sub-ledgers. Cost of materials used flows to COGS accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>No inventory sub-ledger data found for this period.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="004472C4"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2503,7 +2561,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
@@ -2611,13 +2669,13 @@
       <c r="E6" s="7" t="n">
         <v>1438500</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="14" t="n">
         <v>-3000</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1435500</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="15" t="n">
         <v>-0.002085505735140772</v>
       </c>
     </row>
@@ -2651,7 +2709,7 @@
       <c r="G7" s="7" t="n">
         <v>518750</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="15" t="n">
         <v>0.0375</v>
       </c>
     </row>
@@ -2685,7 +2743,7 @@
       <c r="G8" s="7" t="n">
         <v>472500</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="15" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2719,7 +2777,7 @@
       <c r="G9" s="7" t="n">
         <v>113500</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="15" t="n">
         <v>0.135</v>
       </c>
     </row>
@@ -2753,7 +2811,7 @@
       <c r="G10" s="7" t="n">
         <v>1486500</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="15" t="n">
         <v>0.01225740551583248</v>
       </c>
     </row>
@@ -2787,7 +2845,7 @@
       <c r="G11" s="7" t="n">
         <v>54750</v>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2823,7 +2881,7 @@
       <c r="G12" s="7" t="n">
         <v>15000</v>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
